--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484808_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484808_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2303</v>
+        <v>2.3139</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5755</v>
+        <v>2.6856</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3452</v>
+        <v>-0.3717</v>
       </c>
       <c r="G2" t="n">
         <v>2.6121</v>
@@ -610,13 +610,13 @@
         <v>1.5096</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1467</v>
+        <v>1.2304</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6875</v>
+        <v>0.7976</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4592</v>
+        <v>0.4328</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9624</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. CAMARA</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0785</v>
+        <v>0.0814</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0329</v>
+        <v>-0.8914</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1114</v>
+        <v>0.9728</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0169</v>
+        <v>1.2336</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2115</v>
+        <v>1.3359</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1946</v>
+        <v>-0.1024</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0831</v>
+        <v>1.5612</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0831</v>
+        <v>2.1185</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.5573</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.3276</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1284</v>
+        <v>-0.7826</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1946</v>
+        <v>0.455</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1887</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9435</v>
+        <v>-3.774</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7548</v>
+        <v>1.5096</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2651</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5349</v>
+        <v>-0.5463</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8</v>
+        <v>-0.2092</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.8678</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.8678</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6438</v>
+        <v>-0.4858</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3785</v>
+        <v>-0.9932</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7347</v>
+        <v>0.5074</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2336</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3359</v>
+        <v>-1.5362</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1024</v>
+        <v>2.3875</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5612</v>
+        <v>0.6048</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1185</v>
+        <v>-1.4361</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5573</v>
+        <v>2.0409</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3276</v>
+        <v>0.2465</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7826</v>
+        <v>-0.1001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.455</v>
+        <v>0.3466</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.2644</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.774</v>
+        <v>-2.8305</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4808</v>
+        <v>0.229</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0335</v>
+        <v>-0.0127</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4473</v>
+        <v>0.2417</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8678</v>
+        <v>-0.6226</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8678</v>
+        <v>1.2452</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7395</v>
+        <v>-0.6434</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2468</v>
+        <v>-2.2306</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5074</v>
+        <v>1.5872</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8512999999999999</v>
+        <v>-1.7358</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5362</v>
+        <v>0.2841</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3875</v>
+        <v>-2.0199</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6048</v>
+        <v>-0.5214</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4361</v>
+        <v>0.4813</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0409</v>
+        <v>-1.0027</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2465</v>
+        <v>-1.2144</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1001</v>
+        <v>-0.1972</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3466</v>
+        <v>-1.0172</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8305</v>
+        <v>-1.1322</v>
       </c>
       <c r="R5" t="n">
-        <v>1.887</v>
+        <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0247</v>
+        <v>0.5073</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2664</v>
+        <v>0.0646</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2417</v>
+        <v>0.4427</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6226</v>
+        <v>0.019</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2452</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.8678</v>
+        <v>0.6606</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7862</v>
+        <v>-0.7069</v>
       </c>
       <c r="E6" t="n">
         <v>-0.7837</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0026</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-0.07199999999999999</v>
@@ -922,13 +922,13 @@
         <v>0.1887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9029</v>
+        <v>-0.8236</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7266</v>
+        <v>-0.6472</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>O. CAMARA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0919</v>
+        <v>-0.787</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6791</v>
+        <v>-0.6491</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5872</v>
+        <v>-0.1379</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7358</v>
+        <v>1.0169</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2841</v>
+        <v>1.2115</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0199</v>
+        <v>-0.1946</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5214</v>
+        <v>1.0831</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4813</v>
+        <v>1.0831</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.0027</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2144</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1972</v>
+        <v>0.1284</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0172</v>
+        <v>-0.1946</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5661</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1322</v>
+        <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6983</v>
+        <v>0.7548</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0588</v>
+        <v>-0.9736</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3839</v>
+        <v>-0.1472</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4427</v>
+        <v>-0.8265</v>
       </c>
       <c r="V7" t="n">
-        <v>0.019</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W7" t="n">
         <v>-0.6415999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1309</v>
+        <v>-1.4761</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5531</v>
+        <v>0.2608</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.684</v>
+        <v>-1.7369</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1225</v>
@@ -1078,13 +1078,13 @@
         <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0482</v>
+        <v>-0.297</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1793</v>
+        <v>-0.113</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1311</v>
+        <v>-0.184</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3018</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5896</v>
+        <v>-2.6618</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2872</v>
+        <v>-1.9361</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3023</v>
+        <v>-0.7256</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9551</v>
@@ -1156,13 +1156,13 @@
         <v>1.3209</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2386</v>
+        <v>-0.3108</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3498</v>
+        <v>0.0013</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1112</v>
+        <v>-0.3121</v>
       </c>
       <c r="V9" t="n">
         <v>-1.528</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>M. VARELA BARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1193</v>
+        <v>-2.9397</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7012</v>
+        <v>-2.9814</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4181</v>
+        <v>0.0417</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4721</v>
+        <v>-3.8762</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7834</v>
+        <v>-2.4081</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2555</v>
+        <v>-1.4682</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4281</v>
+        <v>-1.9147</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0776</v>
+        <v>-2.6977</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6496</v>
+        <v>0.7829</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9001</v>
+        <v>-1.9615</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2942</v>
+        <v>0.2896</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6059</v>
+        <v>-2.2511</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7548</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1887</v>
+        <v>-3.9627</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9435</v>
+        <v>2.2644</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9117</v>
+        <v>-0.1764</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9406</v>
+        <v>-0.217</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9711</v>
+        <v>0.0407</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4904</v>
+        <v>2.8112</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.113</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4904</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. VARELA BARCIA</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3793</v>
+        <v>-3.7296</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2094</v>
+        <v>-0.3115</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1699</v>
+        <v>-3.4181</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8762</v>
+        <v>-0.4721</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4081</v>
+        <v>0.7834</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4682</v>
+        <v>-1.2555</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9147</v>
+        <v>0.4281</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.6977</v>
+        <v>1.0776</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7829</v>
+        <v>-0.6496</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9615</v>
+        <v>-0.9001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2896</v>
+        <v>-0.2942</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.2511</v>
+        <v>-0.6059</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6983</v>
+        <v>0.7548</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9627</v>
+        <v>-0.1887</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2644</v>
+        <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.616</v>
+        <v>-1.5219</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.445</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.171</v>
+        <v>-0.9711</v>
       </c>
       <c r="V11" t="n">
-        <v>2.8112</v>
+        <v>-2.4904</v>
       </c>
       <c r="W11" t="n">
-        <v>3.113</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3018</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.3287</v>
+        <v>-11.035</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.1244</v>
+        <v>-7.830599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2042</v>
+        <v>-3.204300000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5198</v>
@@ -1363,7 +1363,7 @@
         <v>-3.8974</v>
       </c>
       <c r="J12" t="n">
-        <v>3.883299999999999</v>
+        <v>3.8833</v>
       </c>
       <c r="K12" t="n">
         <v>1.7215</v>
@@ -1375,10 +1375,10 @@
         <v>-6.403</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3438999999999998</v>
+        <v>-0.3438999999999997</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.059100000000001</v>
+        <v>-6.0591</v>
       </c>
       <c r="P12" t="n">
         <v>-3.774</v>
@@ -1390,13 +1390,13 @@
         <v>12.2655</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.1861</v>
+        <v>-2.892100000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1939</v>
+        <v>-0.9</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.9923</v>
+        <v>-1.9922</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8488</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.7623</v>
+        <v>5.4645</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2536</v>
+        <v>3.9869</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5087</v>
+        <v>1.4775</v>
       </c>
       <c r="G13" t="n">
         <v>2.6207</v>
@@ -1468,13 +1468,13 @@
         <v>1.3209</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4624</v>
+        <v>2.1646</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7434</v>
+        <v>1.4767</v>
       </c>
       <c r="U13" t="n">
-        <v>0.719</v>
+        <v>0.6879</v>
       </c>
       <c r="V13" t="n">
         <v>1.2452</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3464</v>
+        <v>5.2833</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0528</v>
+        <v>4.5399</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2936</v>
+        <v>0.7433</v>
       </c>
       <c r="G14" t="n">
         <v>3.2863</v>
@@ -1546,13 +1546,13 @@
         <v>1.1322</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9964</v>
+        <v>-0.0595</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3868</v>
+        <v>0.1003</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6096</v>
+        <v>-0.1598</v>
       </c>
       <c r="V14" t="n">
         <v>1.8678</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3181</v>
+        <v>3.3543</v>
       </c>
       <c r="E15" t="n">
-        <v>1.372</v>
+        <v>1.5668</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9462</v>
+        <v>1.7875</v>
       </c>
       <c r="G15" t="n">
         <v>4.471</v>
@@ -1624,13 +1624,13 @@
         <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1285</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3252</v>
+        <v>-0.1303</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4175</v>
+        <v>0.2587</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2452</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6357</v>
+        <v>2.5286</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7511</v>
+        <v>1.4588</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8846000000000001</v>
+        <v>1.0698</v>
       </c>
       <c r="G16" t="n">
         <v>0.8168</v>
@@ -1702,13 +1702,13 @@
         <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2904</v>
+        <v>0.1833</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2627</v>
+        <v>-0.0296</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0277</v>
+        <v>0.2128</v>
       </c>
       <c r="V16" t="n">
         <v>0.019</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6688</v>
+        <v>2.0693</v>
       </c>
       <c r="E17" t="n">
-        <v>2.046</v>
+        <v>1.9485</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3772</v>
+        <v>0.1207</v>
       </c>
       <c r="G17" t="n">
         <v>2.2932</v>
@@ -1780,13 +1780,13 @@
         <v>1.3209</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0394</v>
+        <v>0.3611</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5472</v>
+        <v>0.4498</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5866</v>
+        <v>-0.0887</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9624</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5354</v>
+        <v>0.6858</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0758</v>
+        <v>-0.2114</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6112</v>
+        <v>0.8971</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1243</v>
+        <v>0.6283</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.055</v>
+        <v>-0.6402</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0694</v>
+        <v>1.2685</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3929</v>
+        <v>0.7259</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-1.2569</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.485</v>
+        <v>1.9828</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7315</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1471</v>
+        <v>0.6167</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5843</v>
+        <v>-0.7143</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8483000000000001</v>
+        <v>-0.2444</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0152</v>
+        <v>-0.2956</v>
       </c>
       <c r="U18" t="n">
-        <v>0.833</v>
+        <v>0.0512</v>
       </c>
       <c r="V18" t="n">
         <v>0.3018</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1289</v>
+        <v>-0.0745</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5037</v>
+        <v>-0.4212</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.3467</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6283</v>
+        <v>-2.8931</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6402</v>
+        <v>0.2935</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2685</v>
+        <v>-3.1866</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7259</v>
+        <v>-1.3272</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2569</v>
+        <v>0.5392</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9828</v>
+        <v>-1.8664</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-1.5659</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6167</v>
+        <v>-0.2457</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7143</v>
+        <v>-1.3202</v>
       </c>
       <c r="P19" t="n">
+        <v>1.887</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.9435</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.9435</v>
+        <v>1.887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8012</v>
+        <v>-0.3326</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5879</v>
+        <v>-0.3391</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2134</v>
+        <v>0.0065</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3018</v>
+        <v>1.2642</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.415</v>
+        <v>-0.1273</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7135</v>
+        <v>-1.3681</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2985</v>
+        <v>1.2408</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8931</v>
+        <v>-2.1243</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2935</v>
+        <v>-1.055</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.1866</v>
+        <v>-1.0694</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3272</v>
+        <v>-1.3929</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5392</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8664</v>
+        <v>-0.485</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5659</v>
+        <v>-0.7315</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2457</v>
+        <v>-0.1471</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3202</v>
+        <v>-0.5843</v>
       </c>
       <c r="P20" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6731</v>
+        <v>0.1856</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6314</v>
+        <v>-0.2771</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0416</v>
+        <v>0.4627</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2642</v>
+        <v>0.3018</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X20" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8115</v>
+        <v>-0.6792</v>
       </c>
       <c r="E21" t="n">
         <v>-0.9741</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1626</v>
+        <v>0.2949</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6203</v>
@@ -2092,13 +2092,13 @@
         <v>0.1887</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6202</v>
+        <v>0.7524</v>
       </c>
       <c r="T21" t="n">
         <v>0.532</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0882</v>
+        <v>0.2205</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0655</v>
+        <v>-2.5406</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.3409</v>
+        <v>-2.3304</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2754</v>
+        <v>-0.2102</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7158</v>
+        <v>-1.2429</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7156</v>
+        <v>-1.0307</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0002</v>
+        <v>-0.2122</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.3623</v>
+        <v>-0.3697</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.7297</v>
+        <v>-0.3953</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6325</v>
+        <v>0.0256</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3535</v>
+        <v>-0.8732</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0141</v>
+        <v>-0.6354</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3676</v>
+        <v>-0.2377</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.774</v>
+        <v>-1.887</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2644</v>
+        <v>2.0757</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9147</v>
+        <v>0.7022</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5501</v>
+        <v>0.2471</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3646</v>
+        <v>0.4551</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2452</v>
+        <v>-2.1886</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2452</v>
+        <v>-0.3208</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7747</v>
+        <v>-3.3361</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3047</v>
+        <v>-5.6332</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.47</v>
+        <v>2.2972</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2429</v>
+        <v>-3.7158</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0307</v>
+        <v>-2.7156</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2122</v>
+        <v>-1.0002</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3697</v>
+        <v>-3.3623</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3953</v>
+        <v>-2.7297</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0256</v>
+        <v>-0.6325</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8732</v>
+        <v>-0.3535</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6354</v>
+        <v>0.0141</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2377</v>
+        <v>-0.3676</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1887</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.887</v>
+        <v>-3.774</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0757</v>
+        <v>2.2644</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.532</v>
+        <v>0.6441</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7272</v>
+        <v>0.2578</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1952</v>
+        <v>0.3863</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1886</v>
+        <v>1.2452</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3208</v>
+        <v>1.2452</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11.3289</v>
+        <v>12.6281</v>
       </c>
       <c r="E24" t="n">
-        <v>2.562800000000001</v>
+        <v>2.562499999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>8.7662</v>
+        <v>10.0653</v>
       </c>
       <c r="G24" t="n">
         <v>2.5199</v>
@@ -2296,13 +2296,13 @@
         <v>-1.377399999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>3.897099999999999</v>
+        <v>3.8971</v>
       </c>
       <c r="J24" t="n">
         <v>6.403</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3441000000000003</v>
+        <v>0.3441000000000005</v>
       </c>
       <c r="L24" t="n">
         <v>6.059200000000001</v>
@@ -2326,13 +2326,13 @@
         <v>16.0395</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1862</v>
+        <v>4.485300000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9921</v>
+        <v>1.992</v>
       </c>
       <c r="U24" t="n">
-        <v>1.194</v>
+        <v>2.4932</v>
       </c>
       <c r="V24" t="n">
         <v>1.8488</v>
